--- a/ERAFONE-STORE-LIST-SEPTEMBER-2026.xlsx
+++ b/ERAFONE-STORE-LIST-SEPTEMBER-2026.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I122"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Nama Store Leader</t>
+          <t>Store Leader</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -530,12 +530,12 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>PANJI ARSY ARYA DILLAH</t>
+          <t>Panji Arsy Arya Dillah</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>+62 887-0770-0830</t>
+          <t>88707700830</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -575,12 +575,12 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Achmad Fauzan</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87877698466</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -665,12 +665,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cahyo Suhendro</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85775411012</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Dyah Laras Safitri</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>(021) 2528112</t>
+          <t>87872297994</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bagus Purbantoro</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>021-40127048</t>
+          <t>81517348893</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -845,12 +845,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Erwin Ilyas</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>021-23581328</t>
+          <t>87776337231</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Firman Saputra</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>021 42901379</t>
+          <t>81563259098</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -935,12 +935,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Khoirul Amirudin</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>021 - 34832347</t>
+          <t>81380064450</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1115,12 +1115,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Citra Lusiana</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81292421449</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Roby Hidayat</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85788706963</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1205,12 +1205,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Adityo A Putra</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>82114003070</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1250,12 +1250,12 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rizki Maulana Sidiq</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85782953531</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1295,12 +1295,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Danang Setyawan</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89693534300</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -1340,12 +1340,12 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Feri Tri Prabowo</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>021-541817</t>
+          <t>87807011995</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Alija Kalifa Akbar</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>021-5239-1560</t>
+          <t>81806161216</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -1475,12 +1475,12 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Yasir</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85894016838</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -1520,12 +1520,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Della Putri Fauza</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81213148340</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Bagas Ajiyanto</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85156549329</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Habibie Al Ghazali</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>881024737300</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1700,12 +1700,12 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Asep Mulyana</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81908120555</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
@@ -1745,7 +1745,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>HAMID SANUSI</t>
+          <t>Hamid Sanusi</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -1790,12 +1790,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ananda Aulia Rochman</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87877603272</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Adit Sukma Anggara</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81351451449</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
@@ -1970,12 +1970,12 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fernaldhy Julian Sanusi</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8568622126</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Theodorus Eltara Ilvian Ristiawan</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>021 73471725</t>
+          <t>81617329666</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calisan</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81510282392</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Abdel Fickry Lain</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81112015550</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>RIKI NOVIANTO</t>
+          <t>Riki Novianto</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2330,12 +2330,12 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ma'ruf Wijaya</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>021 - 6310978</t>
+          <t>83807745664</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
@@ -2465,12 +2465,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ridwan Rifaldo</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>021-5666845</t>
+          <t>81513629299</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rudi Noviansyah</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81919151192</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sigit Dwi Anggoro</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85875091110</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Levia Suci Hardiyanti</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>82114852216</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Agung Kurniawan</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81519440612</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
@@ -2690,12 +2690,12 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Dyna Fitria</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8562000008</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
@@ -2870,12 +2870,12 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muhamad Igfir Refi Syarip</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>895395257767</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Diyanti</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89615673553</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -3005,12 +3005,12 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Iqbal Firdaus</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85959388797</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -3050,12 +3050,12 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muhamad Igfir Refi Syarip</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>895395257767</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muhammad Riduan Wahid</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89603352071</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
@@ -3140,7 +3140,7 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Rama Prasetyo</t>
+          <t>Serpon</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rizki Tazakka</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81779941945</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
@@ -3275,12 +3275,12 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Rama Prasetyo</t>
+          <t>Alfian</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>81291059132</t>
+          <t>85747292806</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mochammad Ramdan Akbar</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85894568558</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mulyana</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>021-59993809</t>
+          <t>87776764678</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
@@ -3410,12 +3410,12 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Andri Sundara</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>021-59993587</t>
+          <t>81318321003</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
@@ -3455,12 +3455,12 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Rezky Nabila</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>+622159990668</t>
+          <t>89678086600</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
@@ -3500,12 +3500,12 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Diki Febriyanto</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>895363851554</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>021-54213507</t>
+          <t>87771807710</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
@@ -3595,7 +3595,7 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>+62 877-7083-6816</t>
+          <t>87770836816</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -3680,12 +3680,12 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ramdani Andika Pramandana</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>82221833394</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -3725,12 +3725,12 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sugianto</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85888026212</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Elvirawati</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87880648402</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
@@ -3815,12 +3815,12 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aditya Anjasmara</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87778274871</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Fahrul Yanuar</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>8985500577</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Teguh Prakoso</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81287162443</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Irfan Supiandi</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81276004200</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
@@ -4130,12 +4130,12 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Edi Suryadi</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85959594176</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>82124749133</t>
+          <t>81315592228</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
@@ -4220,12 +4220,12 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Misbahul Badri</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81283260410</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
@@ -4265,12 +4265,12 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ade Rizky Pajarian</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81574755707</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
@@ -4400,12 +4400,12 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muhammad Dendy</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81281736135</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mahfudin</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>816652158</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
@@ -4470,37 +4470,37 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>G546</t>
+          <t>M093</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>ERABLUE CILEDUG RAYA TANGERANG</t>
+          <t>MEGASTORE RUKO CIPONDOH TANGERANG</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG SELATAN</t>
+          <t>TANGERANG</t>
         </is>
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Megastore</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Cukat Yoga Aditya</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89526719552</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Jl. Ciledug Raya No. 30 RT.006/RW.002, Petukangan Utara, Kec. Pesanggrahan, Kota Tangerang, Banten 15156</t>
+          <t>Jl KH Hasyim Asyhari RT003/RW003 No. 67B Cipondoh Tangerang</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>M093</t>
+          <t>E290</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE RUKO CIPONDOH TANGERANG</t>
+          <t>ERAFONE FRANCHISE RUKO PORIS</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4530,22 +4530,22 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Erafone Megastore</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Cukat Yoga Aditya</t>
+          <t>Hasril Oktama</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>89526719552</t>
+          <t>8976118817</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Jl KH Hasyim Asyhari RT003/RW003 No. 67B Cipondoh Tangerang</t>
+          <t>Jalan Poris indah Raya, Ruko Paradise Eksklusif. Poris Gaga Batu Ceper Tangerang</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>E290</t>
+          <t>E646</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE FRANCHISE RUKO PORIS</t>
+          <t>ERAFONE BATU CEPER</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4575,22 +4575,22 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Saiful Zuhdi</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81284458691</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Jalan Poris indah Raya, Ruko Paradise Eksklusif. Poris Gaga Batu Ceper Tangerang</t>
+          <t>Jl. Halim Perdana Kusuma, RT.002/RW.001, Jurumudi Baru, Kec. Batuceper, Kota Tangerang, Banten 15122</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>E646</t>
+          <t>E119</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE BATU CEPER</t>
+          <t>ERAFONE TANGERANG CITY MALL</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4625,17 +4625,17 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Saiful Zuhdi</t>
+          <t>Mega Nurhatifah, SE</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>81284458691</t>
+          <t>81284456745</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Jl. Halim Perdana Kusuma, RT.002/RW.001, Jurumudi Baru, Kec. Batuceper, Kota Tangerang, Banten 15122</t>
+          <t>Tangerang City Mall Lantai LG, Jl. Jenderal Sudirman No.1, RT.001/RW.005, Babakan, Kec. Tangerang, Kota Tangerang, Banten 15117</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>E119</t>
+          <t>E696</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE TANGERANG CITY MALL</t>
+          <t>ERAFONE MB RASUNA SAID</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4665,22 +4665,22 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Mega Nurhatifah</t>
+          <t>Muhamad Riyanto</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>81284456745</t>
+          <t>87817170393</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Tangerang City Mall Lantai LG, Jl. Jenderal Sudirman No.1, RT.001/RW.005, Babakan, Kec. Tangerang, Kota Tangerang, Banten 15117</t>
+          <t>JL.HR Rasuna Said RT01/RW 02 Pakojan, kec.Pinang, Kota Tangerang, Banten 15142</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>E696</t>
+          <t>M176</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB RASUNA SAID</t>
+          <t>ERAFONE AND MORE KISAMAUN</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone &amp; More</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Muammar Alfis</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81212400080</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>JL.HR Rasuna Said RT01/RW 02 Pakojan, kec.Pinang, Kota Tangerang, Banten 15142</t>
+          <t>Jl Kisamaun No 89G RT/RW 002/007 Kel. Sukasari Kec. Tangerang Kota Tangerang</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>M176</t>
+          <t>E422</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE AND MORE KISAMAUN</t>
+          <t>ERAFONE RUKO M TOHA TANGERANG</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Erafone &amp; More</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Muammar Alfis</t>
+          <t>Michael Roma Nelson</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>+62 812 1240 0080</t>
+          <t>81212456692</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Jl Kisamaun No 89G RT/RW 002/007 Kel. Sukasari Kec. Tangerang Kota Tangerang</t>
+          <t>Jl. Moh. Toha. RT 001/Rw.008 Pabuaran Tumpeng, Kec Karawaci, Kota Tangerang, 15114</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>E422</t>
+          <t>M061</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO M TOHA TANGERANG</t>
+          <t>MEGASTORE RUKO JATIUWUNG</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Megastore</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Santo</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85813046313</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Jl. Moh. Toha. RT 001/Rw.008 Pabuaran Tumpeng, Kec Karawaci, Kota Tangerang, 15114</t>
+          <t>Jl. Gatot Subroto No. A1-A2 RT.001/RW.4, Sangiang Jaya, Kec. Periuk, Kota Tangerang, Banten 15134</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4830,12 +4830,12 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>M061</t>
+          <t>E684</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE RUKO JATIUWUNG</t>
+          <t>ERAFONE RUKO SANGIANG TANGERANG</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -4845,22 +4845,22 @@
       </c>
       <c r="E98" s="2" t="inlineStr">
         <is>
-          <t>Erafone Megastore</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Santo</t>
+          <t>Denny Sanjaya</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>85813046313</t>
+          <t>87880208886</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Jl. Gatot Subroto No. A1-A2 RT.001/RW.4, Sangiang Jaya, Kec. Periuk, Kota Tangerang, Banten 15134</t>
+          <t>Jl. Raya Villa Tangerang Indah RT.003/RW.012 Gebang Raya Kec. Periuk Tangerang 15132</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4875,17 +4875,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>E684</t>
+          <t>E150</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO SANGIANG TANGERANG</t>
+          <t>ERAFONE CILEGON CENTER MALL</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG</t>
+          <t>CILEGON</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4895,17 +4895,17 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Denny Sanjaya</t>
+          <t>Arif Abdurahman Aziz</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>87880208886</t>
+          <t>81287922331</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya Villa Tangerang Indah RT.003/RW.012 Gebang Raya Kec. Periuk Tangerang 15132</t>
+          <t>Cilegon Center Mall Lt 1 No. 14 , Jl. Ahmad Yani No. 11 Sukmajaya, Kec. Jombang, Kota Cilegon, Banten 42416</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -4920,17 +4920,17 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>E150</t>
+          <t>E081</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE CILEGON CENTER MALL</t>
+          <t>ERAFONE MALL OF SERANG</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
         <is>
-          <t>CILEGON</t>
+          <t>SERANG</t>
         </is>
       </c>
       <c r="E100" s="2" t="inlineStr">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Arif Abdurahman Aziz</t>
+          <t>Andi Saputra</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>81287922331</t>
+          <t>87875027979</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Cilegon Center Mall Lt 1 No. 14 , Jl. Ahmad Yani No. 11 Sukmajaya, Kec. Jombang, Kota Cilegon, Banten 42416</t>
+          <t>Mall of Serang Lantai 1 No. 20, Jl. Akses Tol Serang Tim., Panancangan, Kec. Cipocok Jaya, Kota Serang, Banten 42124</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -4965,12 +4965,12 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>E081</t>
+          <t>E209</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MALL OF SERANG</t>
+          <t>ERAFONE RUKO AHMAD YANI SERANG</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -4985,17 +4985,17 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Andi Saputra</t>
+          <t>Depih Harlan</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>87875027979</t>
+          <t>87701418112</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Mall of Serang Lantai 1 No. 20, Jl. Akses Tol Serang Tim., Panancangan, Kec. Cipocok Jaya, Kota Serang, Banten 42124</t>
+          <t>Jl. Jendral Ahmad Yani No.104 RT RW 001/002 Sumurpecung, Kec. Serang, Kota Serang, Banten 42117</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5010,17 +5010,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>E209</t>
+          <t>E194</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO AHMAD YANI SERANG</t>
+          <t>ERAFONE RUKO RANGKASBITUNG</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>SERANG</t>
+          <t>RANGKASBITUNG</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Depih Harlan</t>
+          <t>Fardan Ega Pirmansyah</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>83866359264</t>
+          <t>85694929109</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Jl. Jendral Ahmad Yani No.104 RT RW 001/002 Sumurpecung, Kec. Serang, Kota Serang, Banten 42117</t>
+          <t>Ruko Multatuli Rangkas Bitung, Jl. Multatuli No.95, Muara Ciujung Bar., Kec. Rangkasbitung, Kabupaten Lebak, Banten 42312</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5055,17 +5055,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>E194</t>
+          <t>E308</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO RANGKASBITUNG</t>
+          <t>ERAFONE RUKO MAYOR SAFEI SERANG</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>RANGKASBITUNG</t>
+          <t>SERANG</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5075,17 +5075,17 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Fardan Ega Pirmansyah</t>
+          <t>Wita Gita Widianti</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>85694929109</t>
+          <t>87786221611</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Ruko Multatuli Rangkas Bitung, Jl. Multatuli No.95, Muara Ciujung Bar., Kec. Rangkasbitung, Kabupaten Lebak, Banten 42312</t>
+          <t>Jalan Mayor Safei Serang , Kel Lontarbaru , Kec Serang , Kota Serang Banten Kode POS 42115</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>E308</t>
+          <t>E320</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO MAYOR SAFEI SERANG</t>
+          <t>ERAFONE RUKO PANDEGLANG BANTEN</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>SERANG</t>
+          <t>PANDEGLANG</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Tubagus Hanifan</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>85921222664</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Jalan Mayor Safei Serang , Kel Lontarbaru , Kec Serang , Kota Serang Banten Kode POS 42115</t>
+          <t>Jl. Serang Pandeglang, Kel. Pandeglang Kec. Pandeglang, Kab. Pandeglang, Banten kode Pos 42211</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>E320</t>
+          <t>E589</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO PANDEGLANG BANTEN</t>
+          <t>ERAFONE RUKO PANIMBANG PANDEGLANG</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5165,17 +5165,17 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>TB.HANIFAN</t>
+          <t>Ahmad Hidayatulloh</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>85921222664</t>
+          <t>85778211772</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>Jl. Serang Pandeglang, Kel. Pandeglang Kec. Pandeglang, Kab. Pandeglang, Banten kode Pos 42211</t>
+          <t>JL. Raya Tanjung - Panimbang, Kp. Padahayu RT 01/04 Ds. Panimbang jaya, Kec. Panimbang Kab. Pandeglang 42281</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5190,12 +5190,12 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>E589</t>
+          <t>E499</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO PANIMBANG PANDEGLANG</t>
+          <t>ERAFONE LABUAN PANDEGLANG</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -5210,17 +5210,17 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Arby Rabiul Tsani</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87778810806</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>JL. Raya Tanjung - Panimbang, Kp. Padahayu RT 01/04 Ds. Panimbang jaya, Kec. Panimbang Kab. Pandeglang 42281</t>
+          <t>Jl. Jend. Sudirman No. 99, Muncang Labuan, Kec. Labuang, Pandeglang, Banten 42264</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>E499</t>
+          <t>E544</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE LABUAN PANDEGLANG</t>
+          <t>ERAFONE RUKO MULTIBRAND CILEGON</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>PANDEGLANG</t>
+          <t>CILEGON</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5255,17 +5255,17 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ahmad Khusnul</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>895336274142</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Jl. Jend. Sudirman No. 99, Muncang Labuan, Kec. Labuang, Pandeglang, Banten 42264</t>
+          <t>Jl. Simpang Tiga No.13 RT.06 RW.01 Kel. Ramanuju Kec. Purwakarta Cilegon, Banten 42411</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5280,17 +5280,17 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>E544</t>
+          <t>E821</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO MULTIBRAND CILEGON</t>
+          <t>ERAFONE MB ANYER</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
         <is>
-          <t>CILEGON</t>
+          <t>SERANG</t>
         </is>
       </c>
       <c r="E108" s="2" t="inlineStr">
@@ -5300,17 +5300,17 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Khusnul</t>
+          <t>Ali Rohman</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>895336274142</t>
+          <t>82249001138</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Jl. Simpang Tiga No.13 RT.06 RW.01 Kel. Ramanuju Kec. Purwakarta Cilegon, Banten 42411</t>
+          <t>Jalan Raya Anyer Sirih Kec Anyer Kabupaten Serang Banten 42166</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5325,12 +5325,12 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>E821</t>
+          <t>E822</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB ANYER</t>
+          <t>ERAFONE MB KRAGILAN</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -5345,17 +5345,17 @@
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Marvel Ficky Watuseke</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>0254-7960524</t>
+          <t>81514421196</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Jalan Raya Anyer Sirih Kec Anyer Kabupaten Serang Banten 42166</t>
+          <t>Jalan raya serang- KM 15, Kragilan, kec Kragilan,Kab Serang BANTEN 42184</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5370,37 +5370,37 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>E822</t>
+          <t>E833</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB KRAGILAN</t>
+          <t>ERAFONE RANGKASBITUNG 2</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>SERANG</t>
+          <t>RANGKASBITUNG</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>M Dede Nurjeli</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>0254-7901771</t>
+          <t>85894631045</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>Jalan raya serang- KM 15, Kragilan, kec Kragilan,Kab Serang BANTEN 42184</t>
+          <t>JL. Sunan kalijaga No.325 Kp. Papanggo RT.01 RW.02 Kel. Cijoro Pasir Rangkasbitung</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5415,37 +5415,37 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>E833</t>
+          <t>E879</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RANGKASBITUNG 2</t>
+          <t>ERAFONE MB CIPARE</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>RANGKASBITUNG</t>
+          <t>SERANG</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Hendro Wijaya</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81906450517</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>JL. Sunan kalijaga No.325 Kp. Papanggo RT.01 RW.02 Kel. Cijoro Pasir Rangkasbitung</t>
+          <t>JL. Raya Pandeglang Sempu, Banten Girang RT.001 RW.017 Kel. Cipare Kec. Serang Kota Serang Banten</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5460,37 +5460,37 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>E879</t>
+          <t>M027</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB CIPARE</t>
+          <t>ERAFONE AND MORE CIPUTAT</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>SERANG</t>
+          <t>TANGERANG SELATAN</t>
         </is>
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone &amp; More</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Mochamad Helmi Alatas</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>0254-4078399</t>
+          <t>85155303034</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>JL. Raya Pandeglang Sempu, Banten Girang RT.001 RW.017 Kel. Cipare Kec. Serang Kota Serang Banten</t>
+          <t>Jl. Dewi Sartika No.12 D, Cipayung, Kec. Ciputat, Kota Tangerang Selatan, Banten 15411</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>M027</t>
+          <t>E191</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE AND MORE CIPUTAT</t>
+          <t>ERAFONE RUKO SURYA KENCANA PAMULANG</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5520,22 +5520,22 @@
       </c>
       <c r="E113" s="2" t="inlineStr">
         <is>
-          <t>Erafone &amp; More</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Mochamad Helmi Alatas</t>
+          <t>Muhammad Sidik</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>85117769126</t>
+          <t>85770795112</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Jl. Dewi Sartika No.12 D, Cipayung, Kec. Ciputat, Kota Tangerang Selatan, Banten 15411</t>
+          <t>Jl. Surya Kencana No.60, Pamulang Bar., Kec. Pamulang, Kota Tangerang Selatan, Banten 15417</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>E191</t>
+          <t>F022</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO SURYA KENCANA PAMULANG</t>
+          <t>ERAFONE 2.5 PAMULANG</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5570,17 +5570,17 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Untung</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>87777192252</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Jl. Surya Kencana No.60, Pamulang Bar., Kec. Pamulang, Kota Tangerang Selatan, Banten 15417</t>
+          <t>Jalan siliwangi no. 2 pondok benda, kec. Pamulang, Banten 15417</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>E484</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE 2.5 PAMULANG</t>
+          <t>ERAFONE SERPONG PARADISE WALK</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -5615,17 +5615,17 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Angga Ardian Saputra</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>89608218065</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Jalan siliwangi no. 2 pondok benda, kec. Pamulang, Banten 15417</t>
+          <t>Jalan Graha Raya Boulevard, Paku Jaya, Serpong Utara, Kota Tangerang Selatan, Banten 15220</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -5640,17 +5640,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>E484</t>
+          <t>E087</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE SERPONG PARADISE WALK</t>
+          <t>ERAFONE ITC BSD</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG SELATAN</t>
+          <t>TANGERANG</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5660,17 +5660,17 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Aan</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81990000098</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>Jalan Graha Raya Boulevard, Paku Jaya, Serpong Utara, Kota Tangerang Selatan, Banten 15220</t>
+          <t>BSD City, ITC BSD Lantai 3 D3A-6, Jl. Pahlawan Seribu, Lengkong Wetan, Tangerang, Kota Tangerang Selatan, Banten 15321</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -5685,17 +5685,17 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>E087</t>
+          <t>E941</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE ITC BSD</t>
+          <t>ERAFONE MB RAYA SERPONG</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG</t>
+          <t>TANGERANG SELATAN</t>
         </is>
       </c>
       <c r="E117" s="2" t="inlineStr">
@@ -5705,17 +5705,17 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ari Firdaus Saputra</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>021-5381354</t>
+          <t>85718574849</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>BSD City, ITC BSD Lantai 3 D3A-6, Jl. Pahlawan Seribu, Lengkong Wetan, Tangerang, Kota Tangerang Selatan, Banten 15321</t>
+          <t>Jalan Benda Permai Raya B8/8-B8/9, RT 001, RW 010,Kel/Desa Pondok Benda, Kecamatan Pamulang, Kota Tangerang Selatan, Provinsi Banten</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -5730,12 +5730,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>E941</t>
+          <t>E586</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB RAYA SERPONG</t>
+          <t>ERAFONE RUKO GRAHA RAYA</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5750,17 +5750,17 @@
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>A Rahman</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>895326032806</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Jalan Benda Permai Raya B8/8-B8/9, RT 001, RW 010,Kel/Desa Pondok Benda, Kecamatan Pamulang, Kota Tangerang Selatan, Provinsi Banten</t>
+          <t>Jl. Boulevard Graha Raya NO.B15, Paku Jaya, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15220</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -5775,12 +5775,12 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>E586</t>
+          <t>E834</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO GRAHA RAYA</t>
+          <t>ERAFONE KEDAUNG TANGSEL</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -5790,22 +5790,22 @@
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Samsuri</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>82213538214</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Jl. Boulevard Graha Raya NO.B15, Paku Jaya, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15220</t>
+          <t>Jl. Pondok Cabe Raya No.9, Kec. Pamulang, Kota Tangerang Selatan, Banten 15418</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -5820,37 +5820,37 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>E834</t>
+          <t>E082</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE KEDAUNG TANGSEL</t>
+          <t>ERAFONE LIVING WORLD ALAM SUTERA</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG SELATAN</t>
+          <t>TANGERANG</t>
         </is>
       </c>
       <c r="E120" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Indra Setiawan</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>81519578723</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Jl. Pondok Cabe Raya No.9, Kec. Pamulang, Kota Tangerang Selatan, Banten 15418</t>
+          <t>Living World Alam Sutera 1st floor No.30B Jalan Alam Sutera Boulevard Kav. 21, Pakulonan, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15325</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>E082</t>
+          <t>E088</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE LIVING WORLD ALAM SUTERA</t>
+          <t>ERAFONE AEON MAL BSD CITY</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -5885,65 +5885,20 @@
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
-          <t>Indra Setiawan</t>
+          <t>Gina Tania</t>
         </is>
       </c>
       <c r="G121" s="2" t="inlineStr">
         <is>
-          <t>81519578723</t>
+          <t>85880148262</t>
         </is>
       </c>
       <c r="H121" s="2" t="inlineStr">
         <is>
-          <t>Living World Alam Sutera 1st floor No.30B Jalan Alam Sutera Boulevard Kav. 21, Pakulonan, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15325</t>
+          <t>AEON Mal BSD City Lantai 3 LOT 3-15 Jl. Grand Boulevard BSD City Pagedangan, Kec. Pagedangan, Tangerang, Banten 15345</t>
         </is>
       </c>
       <c r="I121" s="2" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>E088</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>ERAFONE AEON MAL BSD CITY</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
-        <is>
-          <t>TANGERANG</t>
-        </is>
-      </c>
-      <c r="E122" s="2" t="inlineStr">
-        <is>
-          <t>Erafone Multibrand</t>
-        </is>
-      </c>
-      <c r="F122" s="2" t="inlineStr">
-        <is>
-          <t>Gina Tania</t>
-        </is>
-      </c>
-      <c r="G122" s="2" t="inlineStr">
-        <is>
-          <t>85880148262</t>
-        </is>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>AEON Mal BSD City Lantai 3 LOT 3-15 Jl. Grand Boulevard BSD City Pagedangan, Kec. Pagedangan, Tangerang, Banten 15345</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>

--- a/ERAFONE-STORE-LIST-SEPTEMBER-2026.xlsx
+++ b/ERAFONE-STORE-LIST-SEPTEMBER-2026.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I121"/>
+  <dimension ref="A1:I120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2940,12 +2940,12 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>E620</t>
+          <t>M104</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE 2.5 PAJAJARAN PAMULANG</t>
+          <t>MEGASTORE RUKO REMPOA CIPUTAT</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -2955,22 +2955,22 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Megastore</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Heru Bachtiar</t>
+          <t>Iqbal Firdaus</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>83811921019</t>
+          <t>85959388797</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Jl. Pajajaran No.39, Pamulang Barat Kec. Pamulang Tangerang Selatan</t>
+          <t>Jl. Pahlawan No.02 RT.5/RW.3 kelurahan;Rempoa Kecamatan; Ciputat Timur</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
@@ -2985,12 +2985,12 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>M104</t>
+          <t>E321</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE RUKO REMPOA CIPUTAT</t>
+          <t>ERAFONE RUKO SUDIMARA CIPUTAT</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3000,22 +3000,22 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Erafone Megastore</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Iqbal Firdaus</t>
+          <t>Muhamad Igfir Refi Syarip</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>85959388797</t>
+          <t>895395257767</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Jl. Pahlawan No.02 RT.5/RW.3 kelurahan;Rempoa Kecamatan; Ciputat Timur</t>
+          <t>Jl. Jombang Raya No 21 RT/RW 02/02 Kelurahan Jombang, kecamatan Ciputat, Kota Tangerang Selatan, Banten 15414</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
@@ -3030,12 +3030,12 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>E321</t>
+          <t>E704</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO SUDIMARA CIPUTAT</t>
+          <t>ERAFONE RUKO DEWANTARA CIPUTAT</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3050,17 +3050,17 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Muhamad Igfir Refi Syarip</t>
+          <t>Muhammad Riduan Wahid</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>895395257767</t>
+          <t>89603352071</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Jl. Jombang Raya No 21 RT/RW 02/02 Kelurahan Jombang, kecamatan Ciputat, Kota Tangerang Selatan, Banten 15414</t>
+          <t>Jl. Ki Hajar Dewantara No.22, RT.1/RW.3, Ciputat, Kec. Ciputat, Kota Tangerang Selatan, Banten 15411</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>E704</t>
+          <t>E043</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO DEWANTARA CIPUTAT</t>
+          <t>ERAFONE PLAZA BINTARO JAYA</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3095,17 +3095,17 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Muhammad Riduan Wahid</t>
+          <t>Serpon</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>89603352071</t>
+          <t>81291059132</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Jl. Ki Hajar Dewantara No.22, RT.1/RW.3, Ciputat, Kec. Ciputat, Kota Tangerang Selatan, Banten 15411</t>
+          <t>Plaza Bintaro Jaya Lantai 1 No. 12A Jl. Bintaro Utama Sektor 3-A, Pd. Karya, Pd. Aren, Kota Tangerang Selatan, Banten 15225</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
@@ -3120,12 +3120,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>E043</t>
+          <t>E685</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE PLAZA BINTARO JAYA</t>
+          <t>ERAFONE MB PONDOK BETUNG</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3140,17 +3140,17 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Serpon</t>
+          <t>Rizki Tazakka</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>81291059132</t>
+          <t>81779941945</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Plaza Bintaro Jaya Lantai 1 No. 12A Jl. Bintaro Utama Sektor 3-A, Pd. Karya, Pd. Aren, Kota Tangerang Selatan, Banten 15225</t>
+          <t>Jl. Ceger Raya No. 22 B , Kel. Pondok karya Kec. Pondok Aren , Kota Tangerang Selatan , Banten 15225</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>E685</t>
+          <t>E391</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB PONDOK BETUNG</t>
+          <t>ERAFONE RUKO WR SUPRATMAN CIPUTAT</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3185,17 +3185,17 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Rizki Tazakka</t>
+          <t>Heru Bachtiar</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>81779941945</t>
+          <t>83811921019</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Jl. Ceger Raya No. 22 B , Kel. Pondok karya Kec. Pondok Aren , Kota Tangerang Selatan , Banten 15225</t>
+          <t>Jl. WR Supratman No 124 kecamatan. Kecamatan Ciputat Timur. keluraha Cempaka Putih. Banten 15412</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
@@ -3210,17 +3210,17 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>E391</t>
+          <t>E084</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO WR SUPRATMAN CIPUTAT</t>
+          <t>ERAFONE 1 SUPERMALL KARAWACI</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG SELATAN</t>
+          <t>TANGERANG</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3230,17 +3230,17 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Heru Bachtiar</t>
+          <t>Alfian</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>83811921019</t>
+          <t>85747292806</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Jl. WR Supratman No 124 kecamatan. Kecamatan Ciputat Timur. keluraha Cempaka Putih. Banten 15412</t>
+          <t>Supermall Karawaci Lantai LG No.3A-6A E-CENTER, Jl. Boulevard Diponegoro No.105, Bencongan, Kec. Klp. Dua, Kota Tangerang, Banten 15811</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
@@ -3255,37 +3255,37 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>E084</t>
+          <t>M163</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE 1 SUPERMALL KARAWACI</t>
+          <t>ERAFONE AND MORE SERPONG</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG</t>
+          <t>TANGERANG SELATAN</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone &amp; More</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Alfian</t>
+          <t>Mochammad Ramdan Akbar</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>85747292806</t>
+          <t>85894568558</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Supermall Karawaci Lantai LG No.3A-6A E-CENTER, Jl. Boulevard Diponegoro No.105, Bencongan, Kec. Klp. Dua, Kota Tangerang, Banten 15811</t>
+          <t>Jl. MH. Thamrin No.7, Pakualam, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15143</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -3300,37 +3300,37 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>M163</t>
+          <t>E777</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE AND MORE SERPONG</t>
+          <t>ERAFONE MB CIHUNI PAGEDANGAN (ERAFONE CIHUNI GADING SERPONG)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG SELATAN</t>
+          <t>TANGERANG</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Erafone &amp; More</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Mochammad Ramdan Akbar</t>
+          <t>Mulyana</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>85894568558</t>
+          <t>87776764678</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Jl. MH. Thamrin No.7, Pakualam, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15143</t>
+          <t>ruko North sorrento square No.1 Jl.Ir sukarno cihuni,kec pagedangan,kabupaten Tangerang ,Banten 15332</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
@@ -3345,12 +3345,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>E777</t>
+          <t>E873</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB CIHUNI PAGEDANGAN (ERAFONE CIHUNI GADING SERPONG)</t>
+          <t>ERAFONE MB LEGOK</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -3365,17 +3365,17 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Mulyana</t>
+          <t>Andri Sundara</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>87776764678</t>
+          <t>81318321003</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>ruko North sorrento square No.1 Jl.Ir sukarno cihuni,kec pagedangan,kabupaten Tangerang ,Banten 15332</t>
+          <t>Jln. Raya PLP Curug No. 95 Kec. Legok, Kab. Tangerang Banten 15820</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3390,12 +3390,12 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>E873</t>
+          <t>E874</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB LEGOK</t>
+          <t>ERAFONE MULTIBRAND DASANA INDAH</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -3410,17 +3410,17 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>Andri Sundara</t>
+          <t>Rezky Nabila</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>81318321003</t>
+          <t>89678086600</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Jln. Raya PLP Curug No. 95 Kec. Legok, Kab. Tangerang Banten 15820</t>
+          <t>Jln. Raya Dasana Indah Blok SA1 No. 11, Bojong Nangka, Kec. Kelapa Dua Tangerang, Banten 15810</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>E874</t>
+          <t>E813</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MULTIBRAND DASANA INDAH</t>
+          <t>ERAFONE MULTIBRAND SERPONG GARDEN CISAUK</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -3455,17 +3455,17 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Rezky Nabila</t>
+          <t>Diki Febriyanto</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>89678086600</t>
+          <t>895363851554</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Jln. Raya Dasana Indah Blok SA1 No. 11, Bojong Nangka, Kec. Kelapa Dua Tangerang, Banten 15810</t>
+          <t>Jl. Raya Cisauk Lapan Jl. Ruko Serpong Garden ruko 3 No.21, Cibogo, Kec. Cisauk, Kabupaten Tangerang, Banten 15341</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3480,12 +3480,12 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>E813</t>
+          <t>M019</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MULTIBRAND SERPONG GARDEN CISAUK</t>
+          <t>MEGASTORE SUMMARECON MAL SERPONG</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -3495,22 +3495,22 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Megastore</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Diki Febriyanto</t>
+          <t>Niko</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>895363851554</t>
+          <t>87771807710</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya Cisauk Lapan Jl. Ruko Serpong Garden ruko 3 No.21, Cibogo, Kec. Cisauk, Kabupaten Tangerang, Banten 15341</t>
+          <t>Summarecon Mall Serpong Lantai 2F No. 17A, Jalan Gading Serpong Boulevard No.1, No.2 F, Pakulonan Bar., Kec. Klp. Dua, Tangerang, Banten 15810</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
@@ -3525,12 +3525,12 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>M019</t>
+          <t>M013</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE SUMMARECON MAL SERPONG</t>
+          <t>MEGASTORE SUPERMAL KARAWACI</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -3545,17 +3545,17 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>Niko</t>
+          <t>Rudi Herdiyanto</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>87771807710</t>
+          <t>87770836816</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Summarecon Mall Serpong Lantai 2F No. 17A, Jalan Gading Serpong Boulevard No.1, No.2 F, Pakulonan Bar., Kec. Klp. Dua, Tangerang, Banten 15810</t>
+          <t>Supermal Karawaci Lantai 1 Unit FF 51-52 105. Jl. Boulevard Diponegoro No.105, Bencongan, Kec. Klp. Dua, Kota Tangerang, Banten 15811</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3570,12 +3570,12 @@
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>M013</t>
+          <t>M222</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE SUPERMAL KARAWACI</t>
+          <t>ERAFONE AND MORE EASTVARA MALL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -3585,22 +3585,22 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Erafone Megastore</t>
+          <t>Erafone &amp; More</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Rudi Herdiyanto</t>
+          <t>Reno Dharmawan</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>87770836816</t>
+          <t>87808367901</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Supermal Karawaci Lantai 1 Unit FF 51-52 105. Jl. Boulevard Diponegoro No.105, Bencongan, Kec. Klp. Dua, Kota Tangerang, Banten 15811</t>
+          <t>Eastvara Mall, Jl. BSD Boulevard Utara, Cijantra, Kec. Pagedangan, Kabupaten Tangerang, Banten 15854</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
@@ -3615,12 +3615,12 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>M222</t>
+          <t>E369</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE AND MORE EASTVARA MALL</t>
+          <t>ERAFONE FRANCHISE RUKO BOROBUDUR RAYA</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -3630,22 +3630,22 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Erafone &amp; More</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Reno Dharmawan</t>
+          <t>Ramdani Andika Pramandana</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>87808367901</t>
+          <t>82221833394</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Eastvara Mall, Jl. BSD Boulevard Utara, Cijantra, Kec. Pagedangan, Kabupaten Tangerang, Banten 15854</t>
+          <t>Jl. Borobudur Raya Kel, Cibodas Baru, Kec.Cibodas Kota Tangerang</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>E369</t>
+          <t>E370</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE FRANCHISE RUKO BOROBUDUR RAYA</t>
+          <t>ERAFONE FRANCHISE RUKO BERINGIN KARAWACI</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -3680,17 +3680,17 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>Ramdani Andika Pramandana</t>
+          <t>Sugianto</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>82221833394</t>
+          <t>85888026212</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Jl. Borobudur Raya Kel, Cibodas Baru, Kec.Cibodas Kota Tangerang</t>
+          <t>Jl. Beringin Raya Kel. Nusa Jaya, Kec. Tangerang Kota Tangerang</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
@@ -3705,12 +3705,12 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>E370</t>
+          <t>E221</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE FRANCHISE RUKO BERINGIN KARAWACI</t>
+          <t>ERAFONE AND MORE CIPUTRA CITRARAYA TANGERANG</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -3720,22 +3720,22 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone &amp; More</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Sugianto</t>
+          <t>Elvirawati</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>85888026212</t>
+          <t>87880648402</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Jl. Beringin Raya Kel. Nusa Jaya, Kec. Tangerang Kota Tangerang</t>
+          <t>Jl. Citra Raya Boulevard No.38 Mall Citra Lt. 2 unit C 19-12, Ciakar, Kec. Panongan, Kabupaten Tangerang, Banten 15710</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>E221</t>
+          <t>F058</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE AND MORE CIPUTRA CITRARAYA TANGERANG</t>
+          <t>ERAFONE 2.5 TELAGA BESTARI</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -3765,22 +3765,22 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Erafone &amp; More</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>Elvirawati</t>
+          <t>Aditya Anjasmara</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>87880648402</t>
+          <t>87778274871</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Jl. Citra Raya Boulevard No.38 Mall Citra Lt. 2 unit C 19-12, Ciakar, Kec. Panongan, Kabupaten Tangerang, Banten 15710</t>
+          <t>Jl. Taman Palem Raya No.12, Wana Kerta, kec sindang jaya1, Kabupaten Tangerang, Banten 15560</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
@@ -3795,12 +3795,12 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>F058</t>
+          <t>M048</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE 2.5 TELAGA BESTARI</t>
+          <t>MEGASTORE RUKO CIKUPA</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -3810,22 +3810,22 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone Megastore</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Aditya Anjasmara</t>
+          <t>Dede Dermawan</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>87778274871</t>
+          <t>85285954784</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Jl. Taman Palem Raya No.12, Wana Kerta, kec sindang jaya1, Kabupaten Tangerang, Banten 15560</t>
+          <t>Ruko Cikupa, Jl. Raya Serang Balaraja, Sukanagara, Kec. Cikupa, Tangerang, Banten 15710</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>M048</t>
+          <t>M167</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE RUKO CIKUPA</t>
+          <t>ERAFONE AND MORE TELUK NAGA</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -3855,22 +3855,22 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Erafone Megastore</t>
+          <t>Erafone &amp; More</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Dede Dermawan</t>
+          <t>Jatonggo Silitonga</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>85285954784</t>
+          <t>85782286690</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Ruko Cikupa, Jl. Raya Serang Balaraja, Sukanagara, Kec. Cikupa, Tangerang, Banten 15710</t>
+          <t>Kampung Melayu Barat RT 01/RW 02 No. II-C, Kp. Melayu Barat, Kec. Teluknaga, Tangerang Kabupaten, Banten 15510</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
@@ -3885,12 +3885,12 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>M167</t>
+          <t>E627</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE AND MORE TELUK NAGA</t>
+          <t>ERAFONE RUKO CISOKA</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -3900,22 +3900,22 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Erafone &amp; More</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>Jatonggo Silitonga</t>
+          <t>Fahrul Yanuar</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>85782286690</t>
+          <t>8985500577</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Kampung Melayu Barat RT 01/RW 02 No. II-C, Kp. Melayu Barat, Kec. Teluknaga, Tangerang Kabupaten, Banten 15510</t>
+          <t>Jl. Raya Cisoka Adiyasa No .35-36 Rt 001/Rw/001 Kp Lukun Sukatani ,Kec Cisoka Kabupaten Tangerang Banten</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>E627</t>
+          <t>E253</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO CISOKA</t>
+          <t>ERAFONE RUKO CURUG TANGERANG</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -3950,17 +3950,17 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Fahrul Yanuar</t>
+          <t>Teguh Prakoso</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>8985500577</t>
+          <t>81287162443</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya Cisoka Adiyasa No .35-36 Rt 001/Rw/001 Kp Lukun Sukatani ,Kec Cisoka Kabupaten Tangerang Banten</t>
+          <t>Jl. Raya PLP Curug No.16, Suka Bakti, Kec. Curug, Tangerang, Banten 15810</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
@@ -3975,12 +3975,12 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>E253</t>
+          <t>E787</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO CURUG TANGERANG</t>
+          <t>ERAFONE MB TIGARAKSA</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -3995,17 +3995,17 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Teguh Prakoso</t>
+          <t>Nana Pratama</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>81287162443</t>
+          <t>85711100857</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya PLP Curug No.16, Suka Bakti, Kec. Curug, Tangerang, Banten 15810</t>
+          <t>JL. Syeh Mubarok Matagara No.9 RT 001/004, TIGARAKSA TANGERANG Banten 15720</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
@@ -4020,12 +4020,12 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>E787</t>
+          <t>E848</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB TIGARAKSA</t>
+          <t>ERAFONE PASAR KEMIS</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4040,17 +4040,17 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Nana Pratama</t>
+          <t>Irfan Supiandi</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>85711100857</t>
+          <t>81276004200</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>JL. Syeh Mubarok Matagara No.9 RT 001/004, TIGARAKSA TANGERANG Banten 15720</t>
+          <t>JL.Taman Sukamatri Raya A/12 Kel Sukamatri Kec. Pasar Kemis Kab.Tangerang 15560 Banten</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
@@ -4065,12 +4065,12 @@
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>E848</t>
+          <t>E812</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE PASAR KEMIS</t>
+          <t>ERAFONE RUKO KUTABUMI</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4085,17 +4085,17 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>Irfan Supiandi</t>
+          <t>Edi Suryadi</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>81276004200</t>
+          <t>85959594176</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>JL.Taman Sukamatri Raya A/12 Kel Sukamatri Kec. Pasar Kemis Kab.Tangerang 15560 Banten</t>
+          <t>Jl. Raya Regency II Kel. Kuta Jaya Kec. Ps. Kemis Kab. Tangerang 15560</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -4110,12 +4110,12 @@
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>E812</t>
+          <t>E201</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO KUTABUMI</t>
+          <t>ERAFONE RUKO KRESEK BALARAJA</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -4130,17 +4130,17 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>Edi Suryadi</t>
+          <t>Mochamad Ryan Krisdiana</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>85959594176</t>
+          <t>81315592228</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya Regency II Kel. Kuta Jaya Kec. Ps. Kemis Kab. Tangerang 15560</t>
+          <t>Jl. Raya Kresek, Saga, Kec. Balaraja, Tangerang, Banten 15610</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
@@ -4155,12 +4155,12 @@
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>E201</t>
+          <t>E744</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO KRESEK BALARAJA</t>
+          <t>ERAFONE RUKO RAJEG TANGERANG</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -4175,17 +4175,17 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>Mochamad Ryan Krisdiana</t>
+          <t>Misbahul Badri</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>81315592228</t>
+          <t>81283260410</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya Kresek, Saga, Kec. Balaraja, Tangerang, Banten 15610</t>
+          <t>Jl. Raya Ps. Kemis, Mekarsari Kel. Mekarsari Kec. Rajeg Kab. Tangerang Banten 15540.</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>E744</t>
+          <t>F066</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO RAJEG TANGERANG</t>
+          <t>ERAFONE 2.5 SEPATAN</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -4215,22 +4215,22 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>Misbahul Badri</t>
+          <t>Ade Rizky Pajarian</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>81283260410</t>
+          <t>81574755707</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya Ps. Kemis, Mekarsari Kel. Mekarsari Kec. Rajeg Kab. Tangerang Banten 15540.</t>
+          <t>Jl. Raya Mauk Jl. Tangerang Golden City No.3</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -4245,17 +4245,17 @@
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>F066</t>
+          <t>F079</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE 2.5 SEPATAN</t>
+          <t>ERAFONE 2.5 GRAND BATAVIA</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG</t>
+          <t>KABUPATEN TANGERANG</t>
         </is>
       </c>
       <c r="E85" s="2" t="inlineStr">
@@ -4265,17 +4265,17 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>Ade Rizky Pajarian</t>
+          <t>Oktavian Nurrahmat</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>81574755707</t>
+          <t>85932222992</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya Mauk Jl. Tangerang Golden City No.3</t>
+          <t>Jalan Raya Grand Batavia RT02/RW019 Kel.Sindangsari Kec.Pasar Kemis Kab.Tangerang,Banten 15560</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
@@ -4290,37 +4290,37 @@
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>F079</t>
+          <t>M021</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE 2.5 GRAND BATAVIA</t>
+          <t>MEGASTORE RUKO CILEDUG</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>KABUPATEN TANGERANG</t>
+          <t>TANGERANG SELATAN</t>
         </is>
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone Megastore</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>Oktavian Nurrahmat</t>
+          <t>Fahruk Azhara</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>85932222992</t>
+          <t>85822017978</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Jalan Raya Grand Batavia RT02/RW019 Kel.Sindangsari Kec.Pasar Kemis Kab.Tangerang,Banten 15560</t>
+          <t>Jl. Ciledug Raya No. 30 RT.006/RW.002, Petukangan Utara, Kec. Pesanggrahan, Kota Tangerang, Banten 15156</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
@@ -4335,37 +4335,37 @@
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>M021</t>
+          <t>E231</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE RUKO CILEDUG</t>
+          <t>ERAFONE RUKO COKROAMINOTO CILEDUG</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG SELATAN</t>
+          <t>TANGERANG</t>
         </is>
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Erafone Megastore</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>Fahruk Azhara</t>
+          <t>Muhammad Dendy</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>85822017978</t>
+          <t>81281736135</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Jl. Ciledug Raya No. 30 RT.006/RW.002, Petukangan Utara, Kec. Pesanggrahan, Kota Tangerang, Banten 15156</t>
+          <t>Jln. HOS Cokroaminoto No. 29 RT. 002 RW. 004, Karang Timur, Karang Tengah, Ciledug, Tangerang</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -4380,12 +4380,12 @@
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>E231</t>
+          <t>F003</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO COKROAMINOTO CILEDUG</t>
+          <t>Erafone Ciledug 2.5 Raya</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -4400,17 +4400,17 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>Muhammad Dendy</t>
+          <t>Mahfudin</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>81281736135</t>
+          <t>816652158</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Jln. HOS Cokroaminoto No. 29 RT. 002 RW. 004, Karang Timur, Karang Tengah, Ciledug, Tangerang</t>
+          <t>Jl Ciledug Raya No 9 RT/RW 001/009, Larangan Indah, Kec Larangan, Kota Tangerang Banten 15154</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
@@ -4425,12 +4425,12 @@
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>F003</t>
+          <t>M093</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Erafone Ciledug 2.5 Raya</t>
+          <t>MEGASTORE RUKO CIPONDOH TANGERANG</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -4440,22 +4440,22 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Megastore</t>
         </is>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>Mahfudin</t>
+          <t>Cukat Yoga Aditya</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>816652158</t>
+          <t>89526719552</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Jl Ciledug Raya No 9 RT/RW 001/009, Larangan Indah, Kec Larangan, Kota Tangerang Banten 15154</t>
+          <t>Jl KH Hasyim Asyhari RT003/RW003 No. 67B Cipondoh Tangerang</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
@@ -4470,12 +4470,12 @@
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>M093</t>
+          <t>E290</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE RUKO CIPONDOH TANGERANG</t>
+          <t>ERAFONE FRANCHISE RUKO PORIS</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -4485,22 +4485,22 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>Erafone Megastore</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>Cukat Yoga Aditya</t>
+          <t>Hasril Oktama</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>89526719552</t>
+          <t>8976118817</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Jl KH Hasyim Asyhari RT003/RW003 No. 67B Cipondoh Tangerang</t>
+          <t>Jalan Poris indah Raya, Ruko Paradise Eksklusif. Poris Gaga Batu Ceper Tangerang</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
@@ -4515,12 +4515,12 @@
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>E290</t>
+          <t>E646</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE FRANCHISE RUKO PORIS</t>
+          <t>ERAFONE BATU CEPER</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -4530,22 +4530,22 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>Hasril Oktama</t>
+          <t>Saiful Zuhdi</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>8976118817</t>
+          <t>81284458691</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Jalan Poris indah Raya, Ruko Paradise Eksklusif. Poris Gaga Batu Ceper Tangerang</t>
+          <t>Jl. Halim Perdana Kusuma, RT.002/RW.001, Jurumudi Baru, Kec. Batuceper, Kota Tangerang, Banten 15122</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>E646</t>
+          <t>E119</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE BATU CEPER</t>
+          <t>ERAFONE TANGERANG CITY MALL</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -4580,17 +4580,17 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>Saiful Zuhdi</t>
+          <t>Mega Nurhatifah, SE</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>81284458691</t>
+          <t>81284456745</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Jl. Halim Perdana Kusuma, RT.002/RW.001, Jurumudi Baru, Kec. Batuceper, Kota Tangerang, Banten 15122</t>
+          <t>Tangerang City Mall Lantai LG, Jl. Jenderal Sudirman No.1, RT.001/RW.005, Babakan, Kec. Tangerang, Kota Tangerang, Banten 15117</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>E119</t>
+          <t>E696</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE TANGERANG CITY MALL</t>
+          <t>ERAFONE MB RASUNA SAID</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -4620,22 +4620,22 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Mega Nurhatifah, SE</t>
+          <t>Muhamad Riyanto</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>81284456745</t>
+          <t>87817170393</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Tangerang City Mall Lantai LG, Jl. Jenderal Sudirman No.1, RT.001/RW.005, Babakan, Kec. Tangerang, Kota Tangerang, Banten 15117</t>
+          <t>JL.HR Rasuna Said RT01/RW 02 Pakojan, kec.Pinang, Kota Tangerang, Banten 15142</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>E696</t>
+          <t>M176</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB RASUNA SAID</t>
+          <t>ERAFONE AND MORE KISAMAUN</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -4665,22 +4665,22 @@
       </c>
       <c r="E94" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone &amp; More</t>
         </is>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>Muhamad Riyanto</t>
+          <t>Muammar Alfis</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>87817170393</t>
+          <t>81212400080</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>JL.HR Rasuna Said RT01/RW 02 Pakojan, kec.Pinang, Kota Tangerang, Banten 15142</t>
+          <t>Jl Kisamaun No 89G RT/RW 002/007 Kel. Sukasari Kec. Tangerang Kota Tangerang</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>M176</t>
+          <t>E422</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE AND MORE KISAMAUN</t>
+          <t>ERAFONE RUKO M TOHA TANGERANG</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>Erafone &amp; More</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>Muammar Alfis</t>
+          <t>Michael Roma Nelson</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>81212400080</t>
+          <t>81212456692</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Jl Kisamaun No 89G RT/RW 002/007 Kel. Sukasari Kec. Tangerang Kota Tangerang</t>
+          <t>Jl. Moh. Toha. RT 001/Rw.008 Pabuaran Tumpeng, Kec Karawaci, Kota Tangerang, 15114</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>E422</t>
+          <t>M061</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO M TOHA TANGERANG</t>
+          <t>MEGASTORE RUKO JATIUWUNG</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -4755,22 +4755,22 @@
       </c>
       <c r="E96" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Megastore</t>
         </is>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>Michael Roma Nelson</t>
+          <t>Santo</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>81212456692</t>
+          <t>85813046313</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Jl. Moh. Toha. RT 001/Rw.008 Pabuaran Tumpeng, Kec Karawaci, Kota Tangerang, 15114</t>
+          <t>Jl. Gatot Subroto No. A1-A2 RT.001/RW.4, Sangiang Jaya, Kec. Periuk, Kota Tangerang, Banten 15134</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
@@ -4785,12 +4785,12 @@
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>M061</t>
+          <t>E684</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>MEGASTORE RUKO JATIUWUNG</t>
+          <t>ERAFONE RUKO SANGIANG TANGERANG</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="E97" s="2" t="inlineStr">
         <is>
-          <t>Erafone Megastore</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>Santo</t>
+          <t>Denny Sanjaya</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>85813046313</t>
+          <t>87880208886</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Jl. Gatot Subroto No. A1-A2 RT.001/RW.4, Sangiang Jaya, Kec. Periuk, Kota Tangerang, Banten 15134</t>
+          <t>Jl. Raya Villa Tangerang Indah RT.003/RW.012 Gebang Raya Kec. Periuk Tangerang 15132</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
@@ -4830,17 +4830,17 @@
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>E684</t>
+          <t>E150</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO SANGIANG TANGERANG</t>
+          <t>ERAFONE CILEGON CENTER MALL</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG</t>
+          <t>CILEGON</t>
         </is>
       </c>
       <c r="E98" s="2" t="inlineStr">
@@ -4850,17 +4850,17 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>Denny Sanjaya</t>
+          <t>Arif Abdurahman Aziz</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>87880208886</t>
+          <t>81287922331</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Jl. Raya Villa Tangerang Indah RT.003/RW.012 Gebang Raya Kec. Periuk Tangerang 15132</t>
+          <t>Cilegon Center Mall Lt 1 No. 14 , Jl. Ahmad Yani No. 11 Sukmajaya, Kec. Jombang, Kota Cilegon, Banten 42416</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
@@ -4875,17 +4875,17 @@
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>E150</t>
+          <t>E081</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE CILEGON CENTER MALL</t>
+          <t>ERAFONE MALL OF SERANG</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
         <is>
-          <t>CILEGON</t>
+          <t>SERANG</t>
         </is>
       </c>
       <c r="E99" s="2" t="inlineStr">
@@ -4895,17 +4895,17 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>Arif Abdurahman Aziz</t>
+          <t>Andi Saputra</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>81287922331</t>
+          <t>87875027979</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Cilegon Center Mall Lt 1 No. 14 , Jl. Ahmad Yani No. 11 Sukmajaya, Kec. Jombang, Kota Cilegon, Banten 42416</t>
+          <t>Mall of Serang Lantai 1 No. 20, Jl. Akses Tol Serang Tim., Panancangan, Kec. Cipocok Jaya, Kota Serang, Banten 42124</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
@@ -4920,12 +4920,12 @@
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>E081</t>
+          <t>E209</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MALL OF SERANG</t>
+          <t>ERAFONE RUKO AHMAD YANI SERANG</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -4940,17 +4940,17 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>Andi Saputra</t>
+          <t>Depih Harlan</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>87875027979</t>
+          <t>87701418112</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Mall of Serang Lantai 1 No. 20, Jl. Akses Tol Serang Tim., Panancangan, Kec. Cipocok Jaya, Kota Serang, Banten 42124</t>
+          <t>Jl. Jendral Ahmad Yani No.104 RT RW 001/002 Sumurpecung, Kec. Serang, Kota Serang, Banten 42117</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
@@ -4965,17 +4965,17 @@
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>E209</t>
+          <t>E194</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO AHMAD YANI SERANG</t>
+          <t>ERAFONE RUKO RANGKASBITUNG</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>SERANG</t>
+          <t>RANGKASBITUNG</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -4985,17 +4985,17 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>Depih Harlan</t>
+          <t>Fardan Ega Pirmansyah</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>87701418112</t>
+          <t>85694929109</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Jl. Jendral Ahmad Yani No.104 RT RW 001/002 Sumurpecung, Kec. Serang, Kota Serang, Banten 42117</t>
+          <t>Ruko Multatuli Rangkas Bitung, Jl. Multatuli No.95, Muara Ciujung Bar., Kec. Rangkasbitung, Kabupaten Lebak, Banten 42312</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
@@ -5010,17 +5010,17 @@
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>E194</t>
+          <t>E308</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO RANGKASBITUNG</t>
+          <t>ERAFONE RUKO MAYOR SAFEI SERANG</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
         <is>
-          <t>RANGKASBITUNG</t>
+          <t>SERANG</t>
         </is>
       </c>
       <c r="E102" s="2" t="inlineStr">
@@ -5030,17 +5030,17 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>Fardan Ega Pirmansyah</t>
+          <t>Wita Gita Widianti</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>85694929109</t>
+          <t>87786221611</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Ruko Multatuli Rangkas Bitung, Jl. Multatuli No.95, Muara Ciujung Bar., Kec. Rangkasbitung, Kabupaten Lebak, Banten 42312</t>
+          <t>Jalan Mayor Safei Serang , Kel Lontarbaru , Kec Serang , Kota Serang Banten Kode POS 42115</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
@@ -5055,17 +5055,17 @@
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>E308</t>
+          <t>E320</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO MAYOR SAFEI SERANG</t>
+          <t>ERAFONE RUKO PANDEGLANG BANTEN</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
         <is>
-          <t>SERANG</t>
+          <t>PANDEGLANG</t>
         </is>
       </c>
       <c r="E103" s="2" t="inlineStr">
@@ -5075,17 +5075,17 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>Wita Gita Widianti</t>
+          <t>Tubagus Hanifan</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>87786221611</t>
+          <t>85921222664</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>Jalan Mayor Safei Serang , Kel Lontarbaru , Kec Serang , Kota Serang Banten Kode POS 42115</t>
+          <t>Jl. Serang Pandeglang, Kel. Pandeglang Kec. Pandeglang, Kab. Pandeglang, Banten kode Pos 42211</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>E320</t>
+          <t>E589</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO PANDEGLANG BANTEN</t>
+          <t>ERAFONE RUKO PANIMBANG PANDEGLANG</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -5120,17 +5120,17 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>Tubagus Hanifan</t>
+          <t>Ahmad Hidayatulloh</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>85921222664</t>
+          <t>85778211772</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>Jl. Serang Pandeglang, Kel. Pandeglang Kec. Pandeglang, Kab. Pandeglang, Banten kode Pos 42211</t>
+          <t>JL. Raya Tanjung - Panimbang, Kp. Padahayu RT 01/04 Ds. Panimbang jaya, Kec. Panimbang Kab. Pandeglang 42281</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
@@ -5145,12 +5145,12 @@
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>E589</t>
+          <t>E499</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO PANIMBANG PANDEGLANG</t>
+          <t>ERAFONE LABUAN PANDEGLANG</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -5165,17 +5165,17 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Hidayatulloh</t>
+          <t>Arby Rabiul Tsani</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>85778211772</t>
+          <t>87778810806</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>JL. Raya Tanjung - Panimbang, Kp. Padahayu RT 01/04 Ds. Panimbang jaya, Kec. Panimbang Kab. Pandeglang 42281</t>
+          <t>Jl. Jend. Sudirman No. 99, Muncang Labuan, Kec. Labuang, Pandeglang, Banten 42264</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
@@ -5190,17 +5190,17 @@
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>E499</t>
+          <t>E544</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE LABUAN PANDEGLANG</t>
+          <t>ERAFONE RUKO MULTIBRAND CILEGON</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
         <is>
-          <t>PANDEGLANG</t>
+          <t>CILEGON</t>
         </is>
       </c>
       <c r="E106" s="2" t="inlineStr">
@@ -5210,17 +5210,17 @@
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
-          <t>Arby Rabiul Tsani</t>
+          <t>Ahmad Khusnul</t>
         </is>
       </c>
       <c r="G106" s="2" t="inlineStr">
         <is>
-          <t>87778810806</t>
+          <t>895336274142</t>
         </is>
       </c>
       <c r="H106" s="2" t="inlineStr">
         <is>
-          <t>Jl. Jend. Sudirman No. 99, Muncang Labuan, Kec. Labuang, Pandeglang, Banten 42264</t>
+          <t>Jl. Simpang Tiga No.13 RT.06 RW.01 Kel. Ramanuju Kec. Purwakarta Cilegon, Banten 42411</t>
         </is>
       </c>
       <c r="I106" s="2" t="inlineStr">
@@ -5235,17 +5235,17 @@
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>E544</t>
+          <t>E821</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO MULTIBRAND CILEGON</t>
+          <t>ERAFONE MB ANYER</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
         <is>
-          <t>CILEGON</t>
+          <t>SERANG</t>
         </is>
       </c>
       <c r="E107" s="2" t="inlineStr">
@@ -5255,17 +5255,17 @@
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
-          <t>Ahmad Khusnul</t>
+          <t>Ali Rohman</t>
         </is>
       </c>
       <c r="G107" s="2" t="inlineStr">
         <is>
-          <t>895336274142</t>
+          <t>82249001138</t>
         </is>
       </c>
       <c r="H107" s="2" t="inlineStr">
         <is>
-          <t>Jl. Simpang Tiga No.13 RT.06 RW.01 Kel. Ramanuju Kec. Purwakarta Cilegon, Banten 42411</t>
+          <t>Jalan Raya Anyer Sirih Kec Anyer Kabupaten Serang Banten 42166</t>
         </is>
       </c>
       <c r="I107" s="2" t="inlineStr">
@@ -5280,12 +5280,12 @@
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>E821</t>
+          <t>E822</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB ANYER</t>
+          <t>ERAFONE MB KRAGILAN</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -5300,17 +5300,17 @@
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
-          <t>Ali Rohman</t>
+          <t>Marvel Ficky Watuseke</t>
         </is>
       </c>
       <c r="G108" s="2" t="inlineStr">
         <is>
-          <t>82249001138</t>
+          <t>81514421196</t>
         </is>
       </c>
       <c r="H108" s="2" t="inlineStr">
         <is>
-          <t>Jalan Raya Anyer Sirih Kec Anyer Kabupaten Serang Banten 42166</t>
+          <t>Jalan raya serang- KM 15, Kragilan, kec Kragilan,Kab Serang BANTEN 42184</t>
         </is>
       </c>
       <c r="I108" s="2" t="inlineStr">
@@ -5325,37 +5325,37 @@
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>E822</t>
+          <t>E833</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB KRAGILAN</t>
+          <t>ERAFONE RANGKASBITUNG 2</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>SERANG</t>
+          <t>RANGKASBITUNG</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
-          <t>Marvel Ficky Watuseke</t>
+          <t>M Dede Nurjeli</t>
         </is>
       </c>
       <c r="G109" s="2" t="inlineStr">
         <is>
-          <t>81514421196</t>
+          <t>85894631045</t>
         </is>
       </c>
       <c r="H109" s="2" t="inlineStr">
         <is>
-          <t>Jalan raya serang- KM 15, Kragilan, kec Kragilan,Kab Serang BANTEN 42184</t>
+          <t>JL. Sunan kalijaga No.325 Kp. Papanggo RT.01 RW.02 Kel. Cijoro Pasir Rangkasbitung</t>
         </is>
       </c>
       <c r="I109" s="2" t="inlineStr">
@@ -5370,37 +5370,37 @@
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>E833</t>
+          <t>E879</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RANGKASBITUNG 2</t>
+          <t>ERAFONE MB CIPARE</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
         <is>
-          <t>RANGKASBITUNG</t>
+          <t>SERANG</t>
         </is>
       </c>
       <c r="E110" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
-          <t>M Dede Nurjeli</t>
+          <t>Hendro Wijaya</t>
         </is>
       </c>
       <c r="G110" s="2" t="inlineStr">
         <is>
-          <t>85894631045</t>
+          <t>81906450517</t>
         </is>
       </c>
       <c r="H110" s="2" t="inlineStr">
         <is>
-          <t>JL. Sunan kalijaga No.325 Kp. Papanggo RT.01 RW.02 Kel. Cijoro Pasir Rangkasbitung</t>
+          <t>JL. Raya Pandeglang Sempu, Banten Girang RT.001 RW.017 Kel. Cipare Kec. Serang Kota Serang Banten</t>
         </is>
       </c>
       <c r="I110" s="2" t="inlineStr">
@@ -5415,37 +5415,37 @@
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>E879</t>
+          <t>M027</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB CIPARE</t>
+          <t>ERAFONE AND MORE CIPUTAT</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>SERANG</t>
+          <t>TANGERANG SELATAN</t>
         </is>
       </c>
       <c r="E111" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone &amp; More</t>
         </is>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
-          <t>Hendro Wijaya</t>
+          <t>Mochamad Helmi Alatas</t>
         </is>
       </c>
       <c r="G111" s="2" t="inlineStr">
         <is>
-          <t>81906450517</t>
+          <t>85155303034</t>
         </is>
       </c>
       <c r="H111" s="2" t="inlineStr">
         <is>
-          <t>JL. Raya Pandeglang Sempu, Banten Girang RT.001 RW.017 Kel. Cipare Kec. Serang Kota Serang Banten</t>
+          <t>Jl. Dewi Sartika No.12 D, Cipayung, Kec. Ciputat, Kota Tangerang Selatan, Banten 15411</t>
         </is>
       </c>
       <c r="I111" s="2" t="inlineStr">
@@ -5460,12 +5460,12 @@
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>M027</t>
+          <t>E191</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE AND MORE CIPUTAT</t>
+          <t>ERAFONE RUKO SURYA KENCANA PAMULANG</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -5475,22 +5475,22 @@
       </c>
       <c r="E112" s="2" t="inlineStr">
         <is>
-          <t>Erafone &amp; More</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
-          <t>Mochamad Helmi Alatas</t>
+          <t>Muhammad Sidik</t>
         </is>
       </c>
       <c r="G112" s="2" t="inlineStr">
         <is>
-          <t>85155303034</t>
+          <t>85770795112</t>
         </is>
       </c>
       <c r="H112" s="2" t="inlineStr">
         <is>
-          <t>Jl. Dewi Sartika No.12 D, Cipayung, Kec. Ciputat, Kota Tangerang Selatan, Banten 15411</t>
+          <t>Jl. Surya Kencana No.60, Pamulang Bar., Kec. Pamulang, Kota Tangerang Selatan, Banten 15417</t>
         </is>
       </c>
       <c r="I112" s="2" t="inlineStr">
@@ -5505,12 +5505,12 @@
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>E191</t>
+          <t>F022</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO SURYA KENCANA PAMULANG</t>
+          <t>ERAFONE 2.5 PAMULANG</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -5525,17 +5525,17 @@
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
-          <t>Muhammad Sidik</t>
+          <t>Untung</t>
         </is>
       </c>
       <c r="G113" s="2" t="inlineStr">
         <is>
-          <t>85770795112</t>
+          <t>87777192252</t>
         </is>
       </c>
       <c r="H113" s="2" t="inlineStr">
         <is>
-          <t>Jl. Surya Kencana No.60, Pamulang Bar., Kec. Pamulang, Kota Tangerang Selatan, Banten 15417</t>
+          <t>Jalan siliwangi no. 2 pondok benda, kec. Pamulang, Banten 15417</t>
         </is>
       </c>
       <c r="I113" s="2" t="inlineStr">
@@ -5550,12 +5550,12 @@
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>F022</t>
+          <t>E484</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE 2.5 PAMULANG</t>
+          <t>ERAFONE SERPONG PARADISE WALK</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -5570,17 +5570,17 @@
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
-          <t>Untung</t>
+          <t>Angga Ardian Saputra</t>
         </is>
       </c>
       <c r="G114" s="2" t="inlineStr">
         <is>
-          <t>87777192252</t>
+          <t>89608218065</t>
         </is>
       </c>
       <c r="H114" s="2" t="inlineStr">
         <is>
-          <t>Jalan siliwangi no. 2 pondok benda, kec. Pamulang, Banten 15417</t>
+          <t>Jalan Graha Raya Boulevard, Paku Jaya, Serpong Utara, Kota Tangerang Selatan, Banten 15220</t>
         </is>
       </c>
       <c r="I114" s="2" t="inlineStr">
@@ -5595,17 +5595,17 @@
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>E484</t>
+          <t>E087</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE SERPONG PARADISE WALK</t>
+          <t>ERAFONE ITC BSD</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG SELATAN</t>
+          <t>TANGERANG</t>
         </is>
       </c>
       <c r="E115" s="2" t="inlineStr">
@@ -5615,17 +5615,17 @@
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
-          <t>Angga Ardian Saputra</t>
+          <t>Aan</t>
         </is>
       </c>
       <c r="G115" s="2" t="inlineStr">
         <is>
-          <t>89608218065</t>
+          <t>81990000098</t>
         </is>
       </c>
       <c r="H115" s="2" t="inlineStr">
         <is>
-          <t>Jalan Graha Raya Boulevard, Paku Jaya, Serpong Utara, Kota Tangerang Selatan, Banten 15220</t>
+          <t>BSD City, ITC BSD Lantai 3 D3A-6, Jl. Pahlawan Seribu, Lengkong Wetan, Tangerang, Kota Tangerang Selatan, Banten 15321</t>
         </is>
       </c>
       <c r="I115" s="2" t="inlineStr">
@@ -5640,17 +5640,17 @@
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>E087</t>
+          <t>E941</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE ITC BSD</t>
+          <t>ERAFONE MB RAYA SERPONG</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG</t>
+          <t>TANGERANG SELATAN</t>
         </is>
       </c>
       <c r="E116" s="2" t="inlineStr">
@@ -5660,17 +5660,17 @@
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
-          <t>Aan</t>
+          <t>Ari Firdaus Saputra</t>
         </is>
       </c>
       <c r="G116" s="2" t="inlineStr">
         <is>
-          <t>81990000098</t>
+          <t>85718574849</t>
         </is>
       </c>
       <c r="H116" s="2" t="inlineStr">
         <is>
-          <t>BSD City, ITC BSD Lantai 3 D3A-6, Jl. Pahlawan Seribu, Lengkong Wetan, Tangerang, Kota Tangerang Selatan, Banten 15321</t>
+          <t>Jalan Benda Permai Raya B8/8-B8/9, RT 001, RW 010,Kel/Desa Pondok Benda, Kecamatan Pamulang, Kota Tangerang Selatan, Provinsi Banten</t>
         </is>
       </c>
       <c r="I116" s="2" t="inlineStr">
@@ -5685,12 +5685,12 @@
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>E941</t>
+          <t>E586</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE MB RAYA SERPONG</t>
+          <t>ERAFONE RUKO GRAHA RAYA</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -5705,17 +5705,17 @@
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
-          <t>Ari Firdaus Saputra</t>
+          <t>A Rahman</t>
         </is>
       </c>
       <c r="G117" s="2" t="inlineStr">
         <is>
-          <t>85718574849</t>
+          <t>895326032806</t>
         </is>
       </c>
       <c r="H117" s="2" t="inlineStr">
         <is>
-          <t>Jalan Benda Permai Raya B8/8-B8/9, RT 001, RW 010,Kel/Desa Pondok Benda, Kecamatan Pamulang, Kota Tangerang Selatan, Provinsi Banten</t>
+          <t>Jl. Boulevard Graha Raya NO.B15, Paku Jaya, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15220</t>
         </is>
       </c>
       <c r="I117" s="2" t="inlineStr">
@@ -5730,12 +5730,12 @@
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>E586</t>
+          <t>E834</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE RUKO GRAHA RAYA</t>
+          <t>ERAFONE KEDAUNG TANGSEL</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -5745,22 +5745,22 @@
       </c>
       <c r="E118" s="2" t="inlineStr">
         <is>
-          <t>Erafone Multibrand</t>
+          <t>Erafone Franchise</t>
         </is>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
-          <t>A Rahman</t>
+          <t>Samsuri</t>
         </is>
       </c>
       <c r="G118" s="2" t="inlineStr">
         <is>
-          <t>895326032806</t>
+          <t>82213538214</t>
         </is>
       </c>
       <c r="H118" s="2" t="inlineStr">
         <is>
-          <t>Jl. Boulevard Graha Raya NO.B15, Paku Jaya, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15220</t>
+          <t>Jl. Pondok Cabe Raya No.9, Kec. Pamulang, Kota Tangerang Selatan, Banten 15418</t>
         </is>
       </c>
       <c r="I118" s="2" t="inlineStr">
@@ -5775,37 +5775,37 @@
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>E834</t>
+          <t>E082</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE KEDAUNG TANGSEL</t>
+          <t>ERAFONE LIVING WORLD ALAM SUTERA</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
         <is>
-          <t>TANGERANG SELATAN</t>
+          <t>TANGERANG</t>
         </is>
       </c>
       <c r="E119" s="2" t="inlineStr">
         <is>
-          <t>Erafone Franchise</t>
+          <t>Erafone Multibrand</t>
         </is>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
-          <t>Samsuri</t>
+          <t>Indra Setiawan</t>
         </is>
       </c>
       <c r="G119" s="2" t="inlineStr">
         <is>
-          <t>82213538214</t>
+          <t>81519578723</t>
         </is>
       </c>
       <c r="H119" s="2" t="inlineStr">
         <is>
-          <t>Jl. Pondok Cabe Raya No.9, Kec. Pamulang, Kota Tangerang Selatan, Banten 15418</t>
+          <t>Living World Alam Sutera 1st floor No.30B Jalan Alam Sutera Boulevard Kav. 21, Pakulonan, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15325</t>
         </is>
       </c>
       <c r="I119" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>E082</t>
+          <t>E088</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>ERAFONE LIVING WORLD ALAM SUTERA</t>
+          <t>ERAFONE AEON MAL BSD CITY</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -5840,65 +5840,20 @@
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
-          <t>Indra Setiawan</t>
+          <t>Gina Tania</t>
         </is>
       </c>
       <c r="G120" s="2" t="inlineStr">
         <is>
-          <t>81519578723</t>
+          <t>85880148262</t>
         </is>
       </c>
       <c r="H120" s="2" t="inlineStr">
         <is>
-          <t>Living World Alam Sutera 1st floor No.30B Jalan Alam Sutera Boulevard Kav. 21, Pakulonan, Kec. Serpong Utara, Kota Tangerang Selatan, Banten 15325</t>
+          <t>AEON Mal BSD City Lantai 3 LOT 3-15 Jl. Grand Boulevard BSD City Pagedangan, Kec. Pagedangan, Tangerang, Banten 15345</t>
         </is>
       </c>
       <c r="I120" s="2" t="inlineStr">
-        <is>
-          <t>Aktif</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>E088</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>ERAFONE AEON MAL BSD CITY</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>TANGERANG</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="inlineStr">
-        <is>
-          <t>Erafone Multibrand</t>
-        </is>
-      </c>
-      <c r="F121" s="2" t="inlineStr">
-        <is>
-          <t>Gina Tania</t>
-        </is>
-      </c>
-      <c r="G121" s="2" t="inlineStr">
-        <is>
-          <t>85880148262</t>
-        </is>
-      </c>
-      <c r="H121" s="2" t="inlineStr">
-        <is>
-          <t>AEON Mal BSD City Lantai 3 LOT 3-15 Jl. Grand Boulevard BSD City Pagedangan, Kec. Pagedangan, Tangerang, Banten 15345</t>
-        </is>
-      </c>
-      <c r="I121" s="2" t="inlineStr">
         <is>
           <t>Aktif</t>
         </is>
